--- a/data/golden/documents/GD-02_po_polymer.xlsx
+++ b/data/golden/documents/GD-02_po_polymer.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dongguan Polymer Works</t>
+          <t>Heartland Polymer Works</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amount (CNY)</t>
+          <t>Amount (USD)</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>96000</v>
+        <v>13400</v>
       </c>
     </row>
   </sheetData>
